--- a/estandar-b/templates/2-2-matriz-ideas-solucion.xlsx
+++ b/estandar-b/templates/2-2-matriz-ideas-solucion.xlsx
@@ -12,7 +12,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu turno · preguntas guía" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de ideas · evaluación y " sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Matriz de ideas · evaluación y '!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -29,17 +34,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <color rgb="004B5563"/>
-      <sz val="10"/>
+      <sz val="10.5"/>
     </font>
     <font>
-      <name val="Afacad"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -51,8 +57,13 @@
         <fgColor rgb="0028467E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F6FB"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,16 +71,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3E4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3E4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9D3E4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3E4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,7 +473,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mi CompañIA</t>
@@ -482,7 +510,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>MiPyME</t>
@@ -529,7 +557,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -560,17 +588,17 @@
       <c r="C2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Clasificación por novedad, utilidad y factibilidad Puntúa cada idea en los tres criterios. Define qué significa cada nivel (1-5) en el contexto de tu MiPyME.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -586,17 +614,17 @@
       <c r="C4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Idea(s) seleccionada(s) por el cliente ¿Cuál eligió el cliente? ¿Fue una sola idea o una combinación? Documenta el proceso de selección.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -622,7 +650,7 @@
     <col width="29" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>#</t>
@@ -679,18 +707,18 @@
       <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -707,18 +735,18 @@
       <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -735,18 +763,18 @@
       <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="B7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">

--- a/estandar-b/templates/2-2-matriz-ideas-solucion.xlsx
+++ b/estandar-b/templates/2-2-matriz-ideas-solucion.xlsx
@@ -7,14 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tabla 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Referencia de trabajo del F21" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos del documento" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tu turno · preguntas guía" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz de ideas · evaluación y " sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Tabla 1'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Referencia de trabajo del F21'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Datos del documento'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tu turno · preguntas guía'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Matriz de ideas · evaluación y '!$1:$1</definedName>
   </definedNames>
@@ -25,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +36,24 @@
       <name val="Calibri"/>
       <color rgb="004B5563"/>
       <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00529ED7"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0028467E"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -89,9 +106,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -465,28 +494,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="112" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mi CompañIA</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Matriz de ideas de solución validada por el cliente/usuario Manual de Desarrollar con IA · Producto del Elemento 2 · Conceptualizar · Excel</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Producto 2.2 Hoja editable · Excel Mi CompañIA · FUNDES</t>
+          <t>PLANTILLA DE TRABAJO · ESTÁNDAR B</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Matriz de ideas de solución validada por el cliente/usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sobre este template. Tabla comparativa de todas las ideas generadas, evaluadas por novedad, utilidad y factibilidad, con la selección final documentada y validada por el cliente. Excel es el formato natural para esta clase de producto: te permite añadir filas conforme detectes más elementos, ordenar por puntaje y generar gráficas. Llénalo con datos de TU MiPyME real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de trabajo del F21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>•  (a) Contiene el listado de ideas generadas durante el proceso de ideación</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>•  (b) Contiene la descripción breve de cada idea de producto o servicio propuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>•  (c) Incluye una clasificación preliminar de las ideas según criterios de novedad, utilidad y factibilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>•  (d) Especifica las oportunidades de implementación de tecnologías digitales/IA identificadas y validadas por el cliente/usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>•  (e) Especifica la(s) idea(s) seleccionada(s) por el cliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>•  (f) Se presenta en formato de matriz/tabla de análisis, en formato digital/físico, con redacción clara y sin errores ortográficos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="72" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Caso pedagógico Artesanías Tonalli (ilustrativo): Matriz con 6 ideas evaluadas por Lucía y Diego. Criterios: novedad (1-5), utilidad para el negocio (1-5), factibilidad técnica (1-5). Ganadora: "Asistente IA que genera descripción + ficha de producto desde foto" → novedad 4, utilidad 5, factibilidad 4. Segunda: "QR con historia narrada" → descartada por costo de implementación por pieza.</t>
         </is>
       </c>
     </row>
@@ -511,32 +598,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>MiPyME</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr"/>
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr"/>
+      <c r="D1" s="5" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Consultor</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Responsable MiPyME</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -558,73 +645,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Pregunta guía</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Tu respuesta (llena con datos de TU MiPyME)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Listado de ideas con descripción breve Una fila por idea. Describe brevemente qué es y cómo funcionaría.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Clasificación por novedad, utilidad y factibilidad Puntúa cada idea en los tres criterios. Define qué significa cada nivel (1-5) en el contexto de tu MiPyME.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Oportunidades IA validadas por el cliente ¿Qué tecnologías o herramientas de IA vio el cliente como aplicables y deseables para cada idea? ¿Hubo alguna que el cliente rechazó?</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Idea(s) seleccionada(s) por el cliente ¿Cuál eligió el cliente? ¿Fue una sola idea o una combinación? Documenta el proceso de selección.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -646,149 +733,170 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Descripción breve</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Novedad (1-5)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>Utilidad (1-5)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Factibilidad (1-5)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>Score total</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>Seleccionada por el cliente</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="B2" s="6" t="inlineStr"/>
+      <c r="C2" s="6" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
+      <c r="E2" s="6" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
+      <c r="G2" s="6">
+        <f>IF(COUNT(D2:F2)=3,SUM(D2:F2),"")</f>
+        <v/>
+      </c>
+      <c r="H2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr"/>
+      <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="7" t="inlineStr"/>
+      <c r="G3" s="7">
+        <f>IF(COUNT(D3:F3)=3,SUM(D3:F3),"")</f>
+        <v/>
+      </c>
+      <c r="H3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr"/>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
+      <c r="G4" s="6">
+        <f>IF(COUNT(D4:F4)=3,SUM(D4:F4),"")</f>
+        <v/>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7">
+        <f>IF(COUNT(D5:F5)=3,SUM(D5:F5),"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6">
+        <f>IF(COUNT(D6:F6)=3,SUM(D6:F6),"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7">
+        <f>IF(COUNT(D7:F7)=3,SUM(D7:F7),"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="B8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6">
+        <f>IF(COUNT(D8:F8)=3,SUM(D8:F8),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
